--- a/output/pdf_financials_xlsx/IRO.xlsx
+++ b/output/pdf_financials_xlsx/IRO.xlsx
@@ -2406,19 +2406,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.329</v>
@@ -2433,22 +2433,22 @@
         <v>2.463</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.266</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.048</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.603</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>6.214</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>8.085000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2510,19 +2510,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.329</v>
@@ -2537,22 +2537,22 @@
         <v>2.463</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.266</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.048</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.603</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>6.214</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>8.085000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3134,19 +3134,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.901</v>
+        <v>0.057</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.415</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.411</v>
+        <v>0.175</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.539</v>
+        <v>0.209</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.216</v>
+        <v>0.179</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.16</v>
@@ -3161,22 +3161,22 @@
         <v>0.335</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.157</v>
+        <v>0.477</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>9.971</v>
+        <v>7.705</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.758</v>
+        <v>0.71</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.734</v>
+        <v>1.131</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>7.841</v>
+        <v>1.627</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>10.237</v>
+        <v>2.152</v>
       </c>
     </row>
     <row r="49">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -22582,7 +22582,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">

--- a/output/pdf_financials_xlsx/IRO.xlsx
+++ b/output/pdf_financials_xlsx/IRO.xlsx
@@ -5872,28 +5872,28 @@
         <v>0.627</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.537</v>
+        <v>0.323</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0.613</v>
+        <v>0.322</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0.667</v>
+        <v>0.322</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0.829</v>
+        <v>0.322</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="101">
@@ -6517,13 +6517,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.398</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -24594,7 +24594,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -29466,7 +29466,11 @@
           <t>Proceeds on disposal of properties, plant and equipment</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -30823,7 +30827,11 @@
           <t>Proceeds on disposal of properties, plant and equipment</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -32453,7 +32461,11 @@
           <t>Proceeds on disposal of properties, plant and equipment</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -37713,7 +37725,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -39062,7 +39074,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
